--- a/docs/e2e/e2e-test-scenarios-final.xlsx
+++ b/docs/e2e/e2e-test-scenarios-final.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처 매핑" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시나리오'!$A$1:$U$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시나리오'!$A$1:$U$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'삭제·병합 내역'!$A$1:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'출처 매핑'!$A$1:$E$222</definedName>
   </definedNames>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1988,7 +1988,7 @@
       <c r="T13" s="7" t="n"/>
       <c r="U13" s="6" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="131" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>E2E-013</t>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>일부 불일치</t>
+          <t>일치 예상</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -2059,7 +2059,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O14" s="6" t="n"/>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>simulation.spec.ts (E2E-013)</t>
+        </is>
+      </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
           <t>PlannerTest.costOptionIsNotMoreExpensiveAndFastOptionIsNotSlower</t>
@@ -2079,19 +2083,19 @@
       <c r="T14" s="7" t="n"/>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>기본 수량에서는 소요 일수가 운항비 최소 26일 / 가장 빠르게 20일 / 가까운 곳부터 21일이라 기대와 맞는다. 단 배 1척으로 설정한 28개 조합 중 2개(5000/2000/0/8000 → 가장 빠르게 47일 vs 가까운 곳부터 45일, 4001/2001/10001/7001 → 77일 vs 76일)에서 '가까운 곳부터'가 더 빨랐다. 원본 v2의 '운항비 최소 ≤ 가까운 곳부터'(소요 일수) 기대는 기본값 결과(26일 vs 21일)와 맞지 않아 뺐다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>기본 수량에서는 소요 일수가 운항비 최소 26일 / 가장 빠르게 20일 / 가까운 곳부터 21일이라 기대와 맞는다. 단 배 1척으로 설정한 28개 조합 중 2개(5000/2000/0/8000 → 가장 빠르게 47일 vs 가까운 곳부터 45일, 4001/2001/10001/7001 → 77일 vs 76일)에서 '가까운 곳부터'가 더 빨랐다. 원본 v2의 '운항비 최소 ≤ 가까운 곳부터'(소요 일수) 기대는 기본값 결과(26일 vs 21일)와 맞지 않아 뺐다. [분리] 이 시나리오는 기본 수량 기준이다. 불일치 조합(배 1척, 5000/2000/0/8000)은 E2E-013b로 분리했다. 두 번째 조합(4001/2001/10001/7001, 77일 vs 76일)은 아직 자동화하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="125" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>E2E-014</t>
+          <t>E2E-013b</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>E2E-028</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -2101,7 +2105,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>총량이 같아도 나라별 배분을 바꾸면 결과가 달라진다</t>
+          <t>배 1척일 때도 가장 빠르게의 소요 일수가 가장 짧다</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2116,45 +2120,60 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>R1, R2</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>로그인 상태</t>
+          <t>마스터에서 배 척수를 1로 저장해 둠 (끝나면 3으로 원복)</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1. 총량은 같게 두고 나라별 배분을 바꿔 가며 시뮬레이션을 반복한다</t>
+          <t>1. 마스터에서 배 척수를 1로 저장한다
+2. 중국 5,000 / 일본 2,000 / 베트남 0 / 인도네시아 8,000으로 시뮬레이션한다
+3. 세 안의 소요 일수를 읽는다
+4. 정리: 배 척수를 3으로 되돌린다</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>배분마다 소요 일수·비용이 각각 계산되어 표시된다. (배분은 사용자가 정한다)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>일치 예상</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="n"/>
+          <t>'가장 빠르게'의 소요 일수가 세 안 중 가장 짧다.</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>불일치(알려진 결함)</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>불일치 (HJ-S14-08)</t>
+        </is>
+      </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O15" s="6" t="n"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>simulation.spec.ts (E2E-013b, test.fail)</t>
+        </is>
+      </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>PRD 2장 목표 6</t>
+          <t>PRD 6장 경로안의 정의(가장 빠르게 = 총 소요 일수가 가장 짧은 안), HJ-S14-08</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>A:E2E-022</t>
+          <t>E2E-013에서 분리 (C:HJ-S14-08)</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
@@ -2164,152 +2183,239 @@
       </c>
       <c r="S15" s="7" t="n"/>
       <c r="T15" s="7" t="n"/>
-      <c r="U15" s="6" t="n"/>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>E2E-013은 기본 수량에서 통과하므로 불일치 조합만 따로 뗐다. 이 입력에서 가장 빠르게 47일, 가까운 곳부터 45일로 기대와 다르다(직접 재현). 고치기 전에는 Playwright test.fail()로 표시하고, 고치면 표시를 지운다. 마스터를 바꾸므로 원복 필수.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>E2E-014</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>E2E-028</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>3. 경로안 계산·비교</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>총량이 같아도 나라별 배분을 바꾸면 결과가 달라진다</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>R1, R2</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>1. 총량은 같게 두고 나라별 배분을 바꿔 가며 시뮬레이션을 반복한다</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>배분마다 소요 일수·비용이 각각 계산되어 표시된다. (배분은 사용자가 정한다)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>일치 예상</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>PRD 2장 목표 6</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A:E2E-022</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>E2E-015</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>E2E-031 + E2E-032</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>확정하면 상세로 이동하고 메모가 반영된다</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>R3, R7</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>2, 9</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>시뮬레이션 결과가 보이는 상태('운항비 최소')</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>1. 메모를 비운 채 [주문 확정]을 누른다
 2. 새 시뮬레이션 후 메모에 '긴급 주문'을 적고 [주문 확정]을 누른다</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>1: 주문 상세(/orders/{번호})로 이동한다. 상태 '확정', 경로 '운항비 최소', 메모 '-', 작성자 admin. 상태 이력에 1행(이전 '-', 새 '확정', 변경한 사람 admin)이 있다.
 2: 상세의 메모 칸에 '긴급 주문'이 보인다.</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="inlineStr">
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>BatteryService.confirm, OrderFlowTests.confirmThenDetailAndStatusFlow</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>D:E2E-025, A:E2E-030, A:E2E-032, A:E2E-033, B:E2E-014, C:HJ-S05-01, C:HJ-S05-02, C:HJ-S05-03, D:E2E-026, B:E2E-015</t>
         </is>
       </c>
-      <c r="R16" s="7" t="inlineStr">
+      <c r="R17" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S16" s="7" t="n"/>
-      <c r="T16" s="7" t="n"/>
-      <c r="U16" s="6" t="inlineStr">
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="6" t="inlineStr">
         <is>
           <t>주문이 2건 생긴다</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>E2E-016</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>E2E-033 + E2E-034</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>확정한 주문은 선택한 안과 화면에서 본 계산 그대로 저장된다</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>시뮬레이션 결과가 보이는 상태('가장 빠르게' 선택)</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>1. '가장 빠르게'를 선택하고 화면의 소요 일수·생산 원가·운항비·총 비용·배 경로 표를 기록한다
 2. [주문 확정]을 누른다
@@ -2318,189 +2424,189 @@
 5. 다른 시뮬레이션에서 '가까운 곳부터'를 선택해 확정하고 상세의 경로를 확인한다</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>상세의 요약·배 경로·나라별 수량·방문 횟수가 시뮬레이션 때와 완전히 같다.
 목록의 경로 '가장 빠르게', 소요 일수, 총 비용도 같다.
 5: 상세의 경로가 '가까운 곳부터'이고 값이 선택한 안과 같다.</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>BatteryService.confirm(서버 재계산), PRD R3</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>D:E2E-027, A:E2E-031, D:E2E-028</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
+      <c r="R18" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S17" s="7" t="n"/>
-      <c r="T17" s="7" t="n"/>
-      <c r="U17" s="6" t="inlineStr">
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="6" t="inlineStr">
         <is>
           <t>주문이 2건 생긴다</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>E2E-017</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>E2E-036</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>API 로 1,001자 메모·없는 경로 종류를 보내면 이유와 함께 400 이다</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>R3, R9</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>7, 8</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>로그인 상태, 현재 마스터 버전을 /api/master 로 조회</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>1. POST /api/orders 에 메모 1,001자를 보낸다
 2. routeType 을 'XXX' 로 보낸다</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>1: 400, '메모는 1000자 이하로 입력하세요'.
 2: 400, '선택한 경로를 찾을 수 없습니다'.
 두 경우 모두 주문이 생기지 않는다.</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>BatteryService.confirm</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>D:E2E-030</t>
         </is>
       </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="R19" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S18" s="7" t="n"/>
-      <c r="T18" s="7" t="n"/>
-      <c r="U18" s="6" t="inlineStr">
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="6" t="inlineStr">
         <is>
           <t>화면으로는 만들 수 없는 입력</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>E2E-018</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>E2E-037</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>시뮬레이션 뒤 기준 정보가 바뀌면 확정이 거부된다</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>R5, R9</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>2, 3, 8</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>탭(브라우저 컨텍스트) 2개, 마스터 초기값</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>1. 탭 A: 시뮬레이션을 실행한다(확정하지 않는다)
 2. 탭 B: 마스터에서 배 척수를 3 → 2 로 바꿔 저장한다
@@ -2509,113 +2615,22 @@
 5. 정리: 배 척수를 3 으로 되돌린다</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>3: 주문이 만들어지지 않고 '시뮬레이션 이후 마스터 데이터가 바뀌었습니다. 다시 시뮬레이션해 주세요' 가 보인다.
 4: 새 기준으로 확정되어 상세로 이동한다.</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>BatteryService.confirm, OrderFlowTests.confirmFailsWhenMasterChangedAfterSimulation</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>D:E2E-031, A:E2E-050, A:E2E-051, B:E2E-017, C:HJ-S06-01, C:HJ-S06-02</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="n"/>
-      <c r="T19" s="7" t="n"/>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>원복 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>E2E-019</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>E2E-038</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>4. 주문 확정</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>API 로 낡은 마스터 버전을 보내면 409 로 거부된다</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>견고성</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>3, 8</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>로그인 상태</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>1. POST /api/orders 에 masterVersion 을 현재보다 작은 값(0)으로 보낸다</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>409 이고 conflict 가 true, '시뮬레이션 이후 마스터 데이터가 바뀌었습니다…' 메시지가 온다. 주문이 생기지 않는다.</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>일치 예상</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="n"/>
       <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2624,12 +2639,12 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>BatteryService.confirm, AppController.apiError</t>
+          <t>BatteryService.confirm, OrderFlowTests.confirmFailsWhenMasterChangedAfterSimulation</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>D:E2E-032</t>
+          <t>D:E2E-031, A:E2E-050, A:E2E-051, B:E2E-017, C:HJ-S06-01, C:HJ-S06-02</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
@@ -2639,236 +2654,327 @@
       </c>
       <c r="S20" s="7" t="n"/>
       <c r="T20" s="7" t="n"/>
-      <c r="U20" s="6" t="n"/>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>원복 필수</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>E2E-019</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>E2E-038</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>4. 주문 확정</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>API 로 낡은 마스터 버전을 보내면 409 로 거부된다</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>견고성</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>3, 8</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>1. POST /api/orders 에 masterVersion 을 현재보다 작은 값(0)으로 보낸다</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>409 이고 conflict 가 true, '시뮬레이션 이후 마스터 데이터가 바뀌었습니다…' 메시지가 온다. 주문이 생기지 않는다.</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>일치 예상</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>BatteryService.confirm, AppController.apiError</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>D:E2E-032</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>E2E-020</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>E2E-039</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>시뮬레이션만으로는 주문이 생기지 않는다</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>주문 목록의 '전체' 건수를 기록해 둠</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>1. 시뮬레이션을 실행한다
 2. 확정하지 않고 주문 목록으로 이동한다
 3. (참고) 마스터 변경으로 확정이 거부된 경우에도 건수를 확인한다</t>
         </is>
       </c>
-      <c r="K21" s="6" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>주문 건수가 그대로다. 거부된 확정도 주문을 만들지 않는다.</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>PRD R3</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>B:E2E-013</t>
         </is>
       </c>
-      <c r="R21" s="7" t="inlineStr">
+      <c r="R22" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S21" s="7" t="n"/>
-      <c r="T21" s="7" t="n"/>
-      <c r="U21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="S22" s="7" t="n"/>
+      <c r="T22" s="7" t="n"/>
+      <c r="U22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>E2E-021</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>E2E-040</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>확정 요청에 끼워 넣은 계산값은 무시되고 서버가 다시 계산한다</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>로그인 상태</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>1. POST /api/orders에 수량 3,000K×4, 경로안 COST와 함께 totalCost=1, totalDays=1 같은 추가 필드를 보낸다
 2. 만들어진 주문을 목록·상세에서 확인한다</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>추가 필드는 무시되고 서버가 다시 계산한 값(소요 26일 등)으로 저장된다.</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>BatteryService.confirm(서버 재계산)</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>A:E2E-035, C:HJ-S05-07</t>
         </is>
       </c>
-      <c r="R22" s="7" t="inlineStr">
+      <c r="R23" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S22" s="7" t="n"/>
-      <c r="T22" s="7" t="n"/>
-      <c r="U22" s="6" t="inlineStr">
+      <c r="S23" s="7" t="n"/>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>page.request 사용</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>E2E-022</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>E2E-042 + E2E-072</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>4. 주문 확정</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>마스터를 바꿔도 확정한 주문은 그대로고, 새 주문만 새 기준을 따른다</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>R4, R5, R8</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>확정한 주문이 1건, 마스터 초기값</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>1. 주문 상세의 소요 일수·비용·배 경로, '계획에 쓴 마스터 값'(배 척수, 공장 값, 항로)을 기록한다
 2. 마스터에서 중국 하루 최대 생산량 400 → 100, 배 척수 3 → 1로 저장한다
@@ -2877,670 +2983,578 @@
 5. 정리: 마스터를 원복한다</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>3: 상세와 목록의 모든 값이 1에서 기록한 값과 같다. '계획에 쓴 마스터 값'에는 변경 전 값(중국 400, 배 3척)이 그대로 보인다.
 4: 새 주문은 새 기준 값으로, 과거 주문은 확정 당시 값 그대로 표시된다.</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="inlineStr">
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>StoredPlan, OrderFlowTests.masterUpdateBumpsVersionAndKeepsConfirmedPlans</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>D:E2E-033, A:E2E-052, C:HJ-S11-06, A:E2E-053, A:E2E-101</t>
         </is>
       </c>
-      <c r="R23" s="7" t="inlineStr">
+      <c r="R24" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S23" s="7" t="n"/>
-      <c r="T23" s="7" t="n"/>
-      <c r="U23" s="6" t="inlineStr">
+      <c r="S24" s="7" t="n"/>
+      <c r="T24" s="7" t="n"/>
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>원복 필수. 새 주문이 1건 생긴다</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>E2E-023</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>E2E-043</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>5. 주문 목록·상세</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>목록에 필요한 정보가 최신순으로 나온다</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>확정한 주문이 2건 이상</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>1. [주문 목록]을 누른다</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
         <is>
           <t>열: 주문번호, 확정 일시, 총 수량(K), 경로, 소요 일수, 총 비용(억원), 상태, 작성자.
 방금 확정한 주문이 가장 위에 있고 번호가 내림차순이다.</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>orders.html, findAllByOrderByIdDesc</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>D:E2E-034, A:E2E-060, A:E2E-034, B:E2E-006, C:HJ-S05-06</t>
         </is>
       </c>
-      <c r="R24" s="7" t="inlineStr">
+      <c r="R25" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S24" s="7" t="n"/>
-      <c r="T24" s="7" t="n"/>
-      <c r="U24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>E2E-024</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>E2E-044</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>5. 주문 목록·상세</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>상태 필터와 건수가 맞다</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>확정·진행·완료 주문이 각각 1건 이상</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>1. '전체', '확정', '진행', '완료', '취소' 칩의 건수를 읽는다
 2. '진행' 칩을 누른다</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>1: 전체 = 확정+진행+완료+취소 이고 각 건수가 실제 행 수와 같다.
 2: 진행 주문만 보이고 '진행' 칩이 활성 표시다.</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>BatteryService.countByStatus</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>D:E2E-035, A:E2E-061, B:E2E-007, C:HJ-S10-01, C:HJ-S10-02, C:HJ-S10-03, C:HJ-S10-04</t>
         </is>
       </c>
-      <c r="R25" s="7" t="inlineStr">
+      <c r="R26" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S25" s="7" t="n"/>
-      <c r="T25" s="7" t="n"/>
-      <c r="U25" s="6" t="inlineStr">
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="7" t="n"/>
+      <c r="U26" s="6" t="inlineStr">
         <is>
           <t>'취소' 건수는 취소 주문이 삭제돼 늘지 않는다(PRD 7장). 개발 DB 에 옛 취소 건이 남아 있을 수 있음</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>E2E-025</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>E2E-046</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>5. 주문 목록·상세</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>상세에 확정 당시 내용과 이력이 모두 보인다</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>R6, R4</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>4, 9</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>확정한 주문이 1건</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>1. 주문 상세를 연다</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>확정 일시, 작성자, 경로, 메모, 상태 이력, 요약, 나라별 주문 수량·방문 횟수, 배 경로, 일별 생산·비용(펼치기), 계획에 쓴 마스터 값(펼치기), 지도 애니메이션이 모두 있다.
 지도 애니메이션은 자동 재생되지 않는다.</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>order-detail.html, planview.js</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>D:E2E-037, A:E2E-062, C:HJ-S05-04</t>
         </is>
       </c>
-      <c r="R26" s="7" t="inlineStr">
+      <c r="R27" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S26" s="7" t="n"/>
-      <c r="T26" s="7" t="n"/>
-      <c r="U26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>E2E-026</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>E2E-048</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>5. 주문 목록·상세</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>주문 상세에서 일별 재고를 지도 애니메이션으로 볼 수 있다</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>확정한 주문이 1건</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>1. 확정한 주문의 상세를 연다
 2. 지도 애니메이션 슬라이더를 0일, 1일, 3일, 11일로 옮기며 나라별 재고 숫자를 읽는다</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>일별 재고가 나라별로 보인다. 0일은 모든 나라가 0, 1일은 하루 최대 생산량만큼(중국 400·일본 800·베트남 200·인도네시아 300), 3일에는 일본이 0(그날 수거), 11일에는 중국이 0(그날 수거)이다. 수거한 날 그 나라 재고는 0으로 돌아간다.
 일별 생산·비용 표에는 재고 열이 없다. 재고는 지도 애니메이션에서 본다.</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O27" s="6" t="inlineStr">
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>e2e-026.spec.ts (e2e/huju)</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr">
         <is>
           <t>PRD R6(문구 보정 필요), planview.js, anim.js(stockAt)</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>C:HJ-S05-08</t>
         </is>
       </c>
-      <c r="R27" s="7" t="inlineStr">
+      <c r="R28" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S27" s="7" t="n"/>
-      <c r="T27" s="7" t="n"/>
-      <c r="U27" s="6" t="inlineStr">
+      <c r="S28" s="7" t="n"/>
+      <c r="T28" s="7" t="n"/>
+      <c r="U28" s="6" t="inlineStr">
         <is>
           <t>A안으로 변경(2026-10-21). 원래는 일별 표에서 생산·재고를 보는 시나리오였으나 표에는 재고 열이 없고 재고는 지도 애니메이션 슬라이더로 일별 확인된다. 수치는 기본 마스터와 '운항비 최소' 경로안 기준이다. PRD R6 문구를 '일별 생산·재고(재고는 지도 애니메이션)'로 보정할지는 팀 확인이 필요하다.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>E2E-027</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>E2E-050</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>6. 주문 상태 관리</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>확정 → 진행으로 바꾸고 이력이 남는다</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>상태 '확정' 주문의 상세</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>1. [진행(으)로 변경]을 누른다
 2. 확인 창의 문구를 확인하고 [확인]을 누른다</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>1: '진행(으)로 바꿉니다. 계속할까요?' 확인 창이 뜬다.
 2: '상태를 '진행'(으)로 바꿨습니다' 가 보이고 상태 배지가 '진행'이다.
 이력에 '확정 → 진행, 변경한 사람 admin' 행이 추가된다.</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="6" t="inlineStr">
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>BatteryService.changeStatus</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>D:E2E-039, A:E2E-070, A:E2E-080, B:E2E-018, C:HJ-S07-01, C:HJ-S07-03</t>
         </is>
       </c>
-      <c r="R28" s="7" t="inlineStr">
+      <c r="R29" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S28" s="7" t="n"/>
-      <c r="T28" s="7" t="n"/>
-      <c r="U28" s="6" t="inlineStr">
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="6" t="inlineStr">
         <is>
           <t>page.on('dialog') 로 확인 창 처리</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>E2E-028</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>E2E-051</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>6. 주문 상태 관리</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>확인 창에서 취소하면 상태가 바뀌지 않는다</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>상태 '확정' 주문의 상세</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>1. [진행(으)로 변경]을 누른다
 2. 확인 창에서 [취소]를 누른다</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
         <is>
           <t>상태는 '확정'이고 이력 행 수도 그대로다.</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>일치 예상</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>order-detail.html</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>D:E2E-040, C:HJ-S07-02</t>
-        </is>
-      </c>
-      <c r="R29" s="7" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="n"/>
-      <c r="T29" s="7" t="n"/>
-      <c r="U29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>E2E-029</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>E2E-052</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>6. 주문 상태 관리</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>진행 → 완료로 바꾸면 더 바꿀 수 없다</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>상태 '진행' 주문의 상세</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>1. [완료(으)로 변경]을 누르고 확인한다</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>상태 '완료'. 변경 버튼이 사라지고 '최종 상태라 더 바꿀 수 없습니다.' 가 보인다.
-이력이 '확정 → 진행 → 완료' 순서로 3행이다(첫 행의 이전 상태는 '-').</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -3561,12 +3575,12 @@
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>OrderStatus.next, OrderFlowTests.confirmThenDetailAndStatusFlow</t>
+          <t>order-detail.html</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>D:E2E-041, A:E2E-071, B:E2E-019, C:HJ-S07-04</t>
+          <t>D:E2E-040, C:HJ-S07-02</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
@@ -3581,12 +3595,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>E2E-030</t>
+          <t>E2E-029</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>E2E-053</t>
+          <t>E2E-052</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -3596,12 +3610,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>화면에는 허용된 다음 상태 버튼만 있다</t>
+          <t>진행 → 완료로 바꾸면 더 바꿀 수 없다</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -3621,19 +3635,18 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>상태 '확정', '진행' 주문 각 1건</t>
+          <t>상태 '진행' 주문의 상세</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>1. '확정' 주문 상세의 변경 버튼을 본다
-2. '진행' 주문 상세의 변경 버튼을 본다</t>
+          <t>1. [완료(으)로 변경]을 누르고 확인한다</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>1: '진행(으)로 변경', '취소(으)로 변경' 만 있다.
-2: '완료(으)로 변경', '취소(으)로 변경' 만 있다.</t>
+          <t>상태 '완료'. 변경 버튼이 사라지고 '최종 상태라 더 바꿀 수 없습니다.' 가 보인다.
+이력이 '확정 → 진행 → 완료' 순서로 3행이다(첫 행의 이전 상태는 '-').</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -3654,12 +3667,12 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>OrderStatus.next</t>
+          <t>OrderStatus.next, OrderFlowTests.confirmThenDetailAndStatusFlow</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>D:E2E-042, B:E2E-022, C:HJ-S05-05</t>
+          <t>D:E2E-041, A:E2E-071, B:E2E-019, C:HJ-S07-04</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
@@ -3674,148 +3687,241 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>E2E-030</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>E2E-053</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>6. 주문 상태 관리</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>화면에는 허용된 다음 상태 버튼만 있다</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>상태 '확정', '진행' 주문 각 1건</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>1. '확정' 주문 상세의 변경 버튼을 본다
+2. '진행' 주문 상세의 변경 버튼을 본다</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>1: '진행(으)로 변경', '취소(으)로 변경' 만 있다.
+2: '완료(으)로 변경', '취소(으)로 변경' 만 있다.</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>일치 예상</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>OrderStatus.next</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>D:E2E-042, B:E2E-022, C:HJ-S05-05</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="n"/>
+      <c r="T32" s="7" t="n"/>
+      <c r="U32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>E2E-031</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>E2E-054</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>6. 주문 상태 관리</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>허용되지 않은 상태 변경은 직접 요청해도 거부된다</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>9, 8</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>상태 '확정' 주문, 상세의 version 값 확인, 완료 주문 1건</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>1. 로그인한 세션으로 POST /orders/{확정 주문}/status 에 status=COMPLETED, version=현재값을 보낸다
 2. 완료 주문에 status=CANCELED, version=현재값을 보낸다</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="K33" s="6" t="inlineStr">
         <is>
           <t>1: 상태는 '확정' 그대로이고 '확정 상태에서는 완료(으)로 바꿀 수 없습니다' 가 상세에 보인다.
 2: 상태는 '완료' 그대로이고 '완료 상태에서는 취소(으)로 바꿀 수 없습니다' 가 보인다.
 이력 행이 늘지 않는다.</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="6" t="inlineStr">
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>BatteryService.changeStatus, OrderFlowTests</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>D:E2E-043, A:E2E-072, A:E2E-073, A:E2E-074, A:E2E-079, C:HJ-S08-01</t>
         </is>
       </c>
-      <c r="R32" s="7" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S32" s="7" t="n"/>
-      <c r="T32" s="7" t="n"/>
-      <c r="U32" s="6" t="inlineStr">
+      <c r="S33" s="7" t="n"/>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="6" t="inlineStr">
         <is>
           <t>버튼이 없는 요청이라 page.request 사용</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>E2E-032</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>E2E-055 + E2E-057, E2E-060</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>6. 주문 상태 관리</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>확정·진행 주문을 취소하면 목록에서 사라지고 이력은 남는다</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>상태 '확정' 주문</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>1. 상태 '확정' 주문 상세에서 [취소(으)로 변경]을 누르고 확인한다
 2. 주문 목록을 직접 연다
@@ -3824,7 +3930,7 @@
 5. 상태 '진행' 주문으로도 1~2를 반복한다</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
+      <c r="K34" s="6" t="inlineStr">
         <is>
           <t>2: 해당 주문이 목록에 없고 '전체' 건수가 1 줄었다.
 3: 그 주문 번호의 이력이 남아 있고 마지막 행이 '취소'이다. (이력은 주문 번호만 가진 별도 테이블)
@@ -3832,126 +3938,30 @@
 5: 진행 주문도 같은 결과다.</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>BatteryService.changeStatus, PRD 7장, INTENT 5.6</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>D:E2E-044, A:E2E-075, A:E2E-078, B:E2E-020, C:HJ-S09-01, C:HJ-S09-04, D:E2E-046, A:E2E-076, B:E2E-021, C:HJ-S09-03</t>
-        </is>
-      </c>
-      <c r="R33" s="7" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="n"/>
-      <c r="T33" s="7" t="n"/>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>이력은 화면에서 볼 수 없어 DB 조회가 필요하다. 개발 DB에는 삭제 로직 이전에 취소된 주문이 남아 있어 '취소 1'로 보일 수 있으니 새 DB 기준으로 확인한다. 취소 직후 이동 화면은 취소 직후 시나리오(별도)에서 본다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>E2E-033</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>E2E-056</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>6. 주문 상태 관리</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>취소 직후에는 이전 페이지로 이동한다</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>상태 '확정' 주문의 상세(목록에서 들어옴)</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>1. [취소(으)로 변경]을 누르고 확인한다</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>정한 동작: 이전 페이지(주문 목록)로 이동하고 오류 화면이 열리지 않는다.
-현재 구현: 삭제된 주문의 상세(/orders/{번호})로 이동해 HTTP 500 기본 오류 화면(Whitelabel Error Page)이 열린다.</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>불일치(알려진 결함)</t>
-        </is>
-      </c>
-      <c r="M34" s="9" t="inlineStr">
-        <is>
-          <t>불일치 (HJ-S09-02)</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
       <c r="O34" s="6" t="n"/>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>PRD 7장, INTENT 5.6·9장 1번</t>
+          <t>BatteryService.changeStatus, PRD 7장, INTENT 5.6</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>D:E2E-045, A:E2E-077, C:HJ-S09-02</t>
+          <t>D:E2E-044, A:E2E-075, A:E2E-078, B:E2E-020, C:HJ-S09-01, C:HJ-S09-04, D:E2E-046, A:E2E-076, B:E2E-021, C:HJ-S09-03</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
@@ -3963,174 +3973,174 @@
       <c r="T34" s="7" t="n"/>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>고치기 전에는 Playwright test.fail() 로 표시. 고친 뒤 일반 테스트로 전환</t>
+          <t>이력은 화면에서 볼 수 없어 DB 조회가 필요하다. 개발 DB에는 삭제 로직 이전에 취소된 주문이 남아 있어 '취소 1'로 보일 수 있으니 새 DB 기준으로 확인한다. 취소 직후 이동 화면은 취소 직후 시나리오(별도)에서 본다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>E2E-033</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>E2E-056</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>6. 주문 상태 관리</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>취소 직후에는 이전 페이지로 이동한다</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>상태 '확정' 주문의 상세(목록에서 들어옴)</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>1. [취소(으)로 변경]을 누르고 확인한다</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>정한 동작: 이전 페이지(주문 목록)로 이동하고 오류 화면이 열리지 않는다.
+현재 구현: 삭제된 주문의 상세(/orders/{번호})로 이동해 HTTP 500 기본 오류 화면(Whitelabel Error Page)이 열린다.</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>불일치(알려진 결함)</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>불일치 (HJ-S09-02)</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>PRD 7장, INTENT 5.6·9장 1번</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>D:E2E-045, A:E2E-077, C:HJ-S09-02</t>
+        </is>
+      </c>
+      <c r="R35" s="7" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="n"/>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>고치기 전에는 Playwright test.fail() 로 표시. 고친 뒤 일반 테스트로 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>E2E-034</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>E2E-058 + E2E-061</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>6. 주문 상태 관리</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>두 사람이 같은 주문을 동시에 바꾸면 먼저 한 쪽만 인정된다</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>5, 8</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>브라우저 컨텍스트 2개, 상태 '확정' 주문</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>1. 탭 A, 탭 B 에서 같은 주문 상세를 연다
 2. 탭 A: [진행(으)로 변경]을 누르고 확인한다
 3. 탭 B(새로 고침하지 않음): [취소(으)로 변경]을 누르고 확인한다</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>3: 상태는 '진행' 그대로이고 주문이 삭제되지 않는다.
 '다른 사용자가 먼저 이 주문을 변경했습니다. 화면을 새로 고쳐 현재 상태를 확인한 뒤 다시 시도해 주세요' 가 보인다.
 이력에는 탭 A 의 변경만 있다.</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="n"/>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>BatteryService.changeStatus, OrderFlowTests</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>D:E2E-047, A:E2E-090, A:E2E-091, B:E2E-023, C:HJ-S08-02, A:E2E-092</t>
-        </is>
-      </c>
-      <c r="R35" s="7" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="n"/>
-      <c r="T35" s="7" t="n"/>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>같은 시점에 들어온 두 요청을 API로 보내 한쪽만 성공하는지 보는 변형은 이 시나리오와 같은 규칙이라 합쳤다(낙관적 락, version).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>E2E-035</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>E2E-059</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>6. 주문 상태 관리</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>없는 주문 번호로 접속하면 이유를 알려 준다</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>견고성</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>로그인 상태</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>1. /orders/999999 에 접속한다</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>정한 동작: '주문을 찾을 수 없습니다' 같은 안내가 보인다.
-현재 구현: 안내 없이 HTTP 500 기본 오류 화면이 열린다.</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>불일치(알려진 결함)</t>
-        </is>
-      </c>
-      <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>불일치 (HJ-S13-01)</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -4141,12 +4151,12 @@
       <c r="O36" s="6" t="n"/>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>INTENT 9장 2번, BatteryService.getOrder</t>
+          <t>BatteryService.changeStatus, OrderFlowTests</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>D:E2E-048, A:E2E-064, B:E2E-028, C:HJ-S13-01</t>
+          <t>D:E2E-047, A:E2E-090, A:E2E-091, B:E2E-023, C:HJ-S08-02, A:E2E-092</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
@@ -4158,29 +4168,29 @@
       <c r="T36" s="7" t="n"/>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>고치기 전에는 test.fail()</t>
+          <t>같은 시점에 들어온 두 요청을 API로 보내 한쪽만 성공하는지 보는 변형은 이 시나리오와 같은 규칙이라 합쳤다(낙관적 락, version).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>E2E-036</t>
+          <t>E2E-035</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>E2E-062</t>
+          <t>E2E-059</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>7. 기준 정보(마스터) 관리</t>
+          <t>6. 주문 상태 관리</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>마스터 화면에 현재 값이 보인다</t>
+          <t>없는 주문 번호로 접속하면 이유를 알려 준다</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -4190,43 +4200,43 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>견고성</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>로그인 상태, 마스터 초기값</t>
+          <t>로그인 상태</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>1. 상단 [마스터 데이터]를 누른다</t>
+          <t>1. /orders/999999 에 접속한다</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>공장 표(중국 400/4,000/700, 일본 800/2,000/900, 베트남 200/10,000/550, 인도네시아 300/7,000/450), 배 척수 3, 척당 일 운항비 1, 항로 표(항해 일수)가 보인다.
-'값을 바꿔도 이미 확정한 주문의 계획은 바뀌지 않습니다' 안내가 있다.</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>일치 예상</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>정한 동작: '주문을 찾을 수 없습니다' 같은 안내가 보인다.
+현재 구현: 안내 없이 HTTP 500 기본 오류 화면이 열린다.</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>불일치(알려진 결함)</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>불일치 (HJ-S13-01)</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -4237,12 +4247,12 @@
       <c r="O37" s="6" t="n"/>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>master.html, BatteryService.initDefaults</t>
+          <t>INTENT 9장 2번, BatteryService.getOrder</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>D:E2E-049, A:E2E-040, A:E2E-047, B:E2E-024, C:HJ-S11-01</t>
+          <t>D:E2E-048, A:E2E-064, B:E2E-028, C:HJ-S13-01</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
@@ -4254,57 +4264,153 @@
       <c r="T37" s="7" t="n"/>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>초기값이 아닌 DB 에서는 기대 값이 다를 수 있음</t>
+          <t>고치기 전에는 test.fail()</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>E2E-036</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>E2E-062</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>7. 기준 정보(마스터) 관리</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>마스터 화면에 현재 값이 보인다</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태, 마스터 초기값</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>1. 상단 [마스터 데이터]를 누른다</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>공장 표(중국 400/4,000/700, 일본 800/2,000/900, 베트남 200/10,000/550, 인도네시아 300/7,000/450), 배 척수 3, 척당 일 운항비 1, 항로 표(항해 일수)가 보인다.
+'값을 바꿔도 이미 확정한 주문의 계획은 바뀌지 않습니다' 안내가 있다.</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>일치 예상</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>master.html, BatteryService.initDefaults</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>D:E2E-049, A:E2E-040, A:E2E-047, B:E2E-024, C:HJ-S11-01</t>
+        </is>
+      </c>
+      <c r="R38" s="7" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="n"/>
+      <c r="T38" s="7" t="n"/>
+      <c r="U38" s="6" t="inlineStr">
+        <is>
+          <t>초기값이 아닌 DB 에서는 기대 값이 다를 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>E2E-037</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>E2E-063</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>7. 기준 정보(마스터) 관리</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>값을 바꿔 저장하면 유지되고 버전이 오른다</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>13, 3</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>마스터 화면</t>
         </is>
       </c>
-      <c r="J38" s="6" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>1. GET /api/master 로 version 을 기록한다
 2. 중국 하루 최대 생산량을 400 → 500 으로 바꿔 [저장]한다
@@ -4312,98 +4418,98 @@
 4. 정리: 400 으로 되돌려 저장한다</t>
         </is>
       </c>
-      <c r="K38" s="6" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>2: '마스터 데이터를 저장했습니다' 가 보인다.
 3: 중국 하루 최대가 500 으로 남아 있고 version 이 1 올라 있다.</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O38" s="6" t="n"/>
-      <c r="P38" s="6" t="inlineStr">
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>BatteryService.updateMaster, OrderFlowTests.masterUpdateBumpsVersionAndKeepsConfirmedPlans</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>D:E2E-050, A:E2E-041, B:E2E-025, C:HJ-S11-04, C:HJ-S11-08</t>
         </is>
       </c>
-      <c r="R38" s="7" t="inlineStr">
+      <c r="R39" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S38" s="7" t="n"/>
-      <c r="T38" s="7" t="n"/>
-      <c r="U38" s="6" t="inlineStr">
+      <c r="S39" s="7" t="n"/>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="6" t="inlineStr">
         <is>
           <t>원복 필수</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>E2E-038</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>E2E-064</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>7. 기준 정보(마스터) 관리</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>바뀐 마스터 값이 새 시뮬레이션에 반영된다</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>마스터 화면</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>1. 기본 수량으로 시뮬레이션해 '운항비 최소'의 소요 일수를 기록한다
 2. 마스터에서 중국 하루 최대 생산량을 400 → 100 으로 저장한다
@@ -4411,104 +4517,104 @@
 4. 정리: 400 으로 원복한다</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>3: 소요 일수가 늘어나거나 같고, '계획에 쓴 마스터 값'의 중국 하루 최대가 100 으로 표시된다. 코드 수정 없이 값만으로 결과가 바뀐다.</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O39" s="6" t="n"/>
-      <c r="P39" s="6" t="inlineStr">
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>PRD R8</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>D:E2E-051, A:E2E-042, B:E2E-027, C:HJ-S11-02, C:HJ-S11-03, C:HJ-S11-05, C:HJ-S11-07</t>
         </is>
       </c>
-      <c r="R39" s="7" t="inlineStr">
+      <c r="R40" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S39" s="7" t="n"/>
-      <c r="T39" s="7" t="n"/>
-      <c r="U39" s="6" t="inlineStr">
+      <c r="S40" s="7" t="n"/>
+      <c r="T40" s="7" t="n"/>
+      <c r="U40" s="6" t="inlineStr">
         <is>
           <t>원복 필수</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>E2E-039</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>E2E-065 + E2E-066</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>7. 기준 정보(마스터) 관리</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>잘못된 운항비(숫자 아님·0·원 단위 아님)는 저장되지 않는다</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>7, 8, 12</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>마스터 화면</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>1. 척당 일 운항비에 abc를 넣고 [저장]한 뒤 화면을 새로 고친다
 2. 0을 넣고 [저장]한다
 3. 1.000000001을 넣고 [저장]한다</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
+      <c r="K41" s="6" t="inlineStr">
         <is>
           <t>1: '저장하지 않았습니다. 아래 값을 확인하세요.'와 '척당 일 운항비(억 원)는 숫자로 입력하세요'가 보이고 입력한 값이 그대로 남는다. 새로 고치면 이전에 저장된 값이 보인다.
 2: '척당 일 운항비는 0보다 커야 합니다'.
@@ -4516,92 +4622,92 @@
 세 경우 모두 저장되지 않는다.</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O40" s="6" t="n"/>
-      <c r="P40" s="6" t="inlineStr">
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>BatteryService.updateMaster, OrderFlowTests.invalidMasterIsNotSaved</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>D:E2E-052, A:E2E-043, B:E2E-026, C:HJ-S12-02, D:E2E-053, A:E2E-046, C:HJ-S12-03, C:HJ-S12-05</t>
         </is>
       </c>
-      <c r="R40" s="7" t="inlineStr">
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S40" s="7" t="n"/>
-      <c r="T40" s="7" t="n"/>
-      <c r="U40" s="6" t="inlineStr">
+      <c r="S41" s="7" t="n"/>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="6" t="inlineStr">
         <is>
           <t>금액은 원 단위 정수(INTENT 원칙 12)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>E2E-040</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>E2E-067</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>7. 기준 정보(마스터) 관리</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>잘못된 값이 섞이면 아무것도 저장되지 않고 오류가 모두 나온다</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>견고성</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>마스터 화면, 브라우저 기본 검증은 끈다(noValidate)</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>1. 중국 하루 최대 생산량을 500(올바른 값)으로 바꾼다
 2. 같은 화면에서 배 척수 5, 일본 재고 상한 0, 베트남 항해 일수 400 을 넣는다
@@ -4609,98 +4715,98 @@
 4. 새로 고친다</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>3: 오류 3건이 한꺼번에 나열된다(예: '배 척수은(는) 1 이상 4 이하의 정수여야 합니다').
 4: 중국 하루 최대는 500 이 아니라 원래 값(400)이다. 올바른 값도 저장되지 않는다.</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O41" s="6" t="n"/>
-      <c r="P41" s="6" t="inlineStr">
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>BatteryService.updateMaster, INTENT 원칙 7</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>D:E2E-054, A:E2E-044, A:E2E-045, C:HJ-S12-01, C:HJ-S12-04</t>
         </is>
       </c>
-      <c r="R41" s="7" t="inlineStr">
+      <c r="R42" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S41" s="7" t="n"/>
-      <c r="T41" s="7" t="n"/>
-      <c r="U41" s="6" t="inlineStr">
+      <c r="S42" s="7" t="n"/>
+      <c r="T42" s="7" t="n"/>
+      <c r="U42" s="6" t="inlineStr">
         <is>
           <t>숫자 칸의 min/max 속성이 먼저 막을 수 있어 noValidate 처리 필요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>E2E-041</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>E2E-069</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>8. 대표 종단 흐름</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>로그인부터 완료·로그아웃까지 한 번에 진행한다</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>R1, R2, R3, R6, R7, R11</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>1, 2, 4, 9</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>로그아웃 상태, 마스터 초기값</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>1. admin/admin 으로 로그인한다
 2. [주문 추가]에서 기본 수량으로 시뮬레이션한다
@@ -4710,7 +4816,7 @@
 6. 로그아웃한다</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>3: 상세 화면, 상태 '확정'.
 4: 이력이 '확정 → 진행 → 완료' 3행이고 더 바꿀 수 없다.
@@ -4718,45 +4824,45 @@
 6: 로그인 화면으로 돌아간다.</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>일치 예상</t>
         </is>
       </c>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O42" s="6" t="n"/>
-      <c r="P42" s="6" t="inlineStr">
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>OrderFlowTests.confirmThenDetailAndStatusFlow</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>D:E2E-056, A:E2E-100</t>
         </is>
       </c>
-      <c r="R42" s="7" t="inlineStr">
+      <c r="R43" s="7" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="S42" s="7" t="n"/>
-      <c r="T42" s="7" t="n"/>
-      <c r="U42" s="6" t="inlineStr">
+      <c r="S43" s="7" t="n"/>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="6" t="inlineStr">
         <is>
           <t>대표 스모크 테스트</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U42"/>
+  <autoFilter ref="A1:U43"/>
   <dataValidations count="1">
-    <dataValidation sqref="R2:R42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="R2:R43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"미실행,통과,실패,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4846,7 +4952,7 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTA(시나리오!$A$2:$A$42)</f>
+        <f>COUNTA(시나리오!$A$2:$A$43)</f>
         <v/>
       </c>
     </row>
@@ -4902,19 +5008,19 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A13)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A13)</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A13,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A13,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A13,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A13,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E13" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A13,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A13,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -4925,19 +5031,19 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A14)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A14)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A14,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A14,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A14,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A14,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A14,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A14,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -4948,19 +5054,19 @@
         </is>
       </c>
       <c r="B15" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A15)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A15)</f>
         <v/>
       </c>
       <c r="C15" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A15,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A15,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A15,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A15,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E15" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A15,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A15,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -4971,19 +5077,19 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A16)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A16)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A16,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A16,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A16,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A16,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A16,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A16,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -4994,19 +5100,19 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A17)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A17)</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A17,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A17,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A17,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A17,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E17" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A17,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A17,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -5017,19 +5123,19 @@
         </is>
       </c>
       <c r="B18" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A18)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A18)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A18,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A18,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D18" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A18,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A18,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E18" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A18,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A18,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -5040,19 +5146,19 @@
         </is>
       </c>
       <c r="B19" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A19)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A19)</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A19,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A19,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D19" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A19,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A19,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E19" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A19,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A19,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -5063,19 +5169,19 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$42,A20)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$43,A20)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A20,시나리오!$E$2:$E$42,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A20,시나리오!$E$2:$E$43,"상")</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A20,시나리오!$E$2:$E$42,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A20,시나리오!$E$2:$E$43,"중")</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$42,$A20,시나리오!$E$2:$E$42,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$43,$A20,시나리오!$E$2:$E$43,"하")</f>
         <v/>
       </c>
     </row>
@@ -5128,7 +5234,7 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$42,A25)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$43,A25)</f>
         <v/>
       </c>
     </row>
@@ -5139,7 +5245,7 @@
         </is>
       </c>
       <c r="B26" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$42,A26)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$43,A26)</f>
         <v/>
       </c>
     </row>
@@ -5150,7 +5256,7 @@
         </is>
       </c>
       <c r="B27" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$42,A27)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$43,A27)</f>
         <v/>
       </c>
     </row>
@@ -5161,7 +5267,7 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$42,A28)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$43,A28)</f>
         <v/>
       </c>
     </row>
@@ -5172,7 +5278,7 @@
         </is>
       </c>
       <c r="B29" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$42,A29)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$43,A29)</f>
         <v/>
       </c>
     </row>
@@ -5202,7 +5308,7 @@
         </is>
       </c>
       <c r="B33" s="14">
-        <f>COUNTIF(시나리오!$N$2:$N$42,"Y")</f>
+        <f>COUNTIF(시나리오!$N$2:$N$43,"Y")</f>
         <v/>
       </c>
     </row>
@@ -5213,7 +5319,7 @@
         </is>
       </c>
       <c r="B34" s="14">
-        <f>COUNTIF(시나리오!$N$2:$N$42,"N")</f>
+        <f>COUNTIF(시나리오!$N$2:$N$43,"N")</f>
         <v/>
       </c>
     </row>
@@ -5224,7 +5330,7 @@
         </is>
       </c>
       <c r="B35" s="14">
-        <f>COUNTA(시나리오!$O$2:$O$42)</f>
+        <f>COUNTA(시나리오!$O$2:$O$43)</f>
         <v/>
       </c>
     </row>
@@ -5254,7 +5360,7 @@
         </is>
       </c>
       <c r="B39" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$42,A39)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$43,A39)</f>
         <v/>
       </c>
     </row>
@@ -5265,7 +5371,7 @@
         </is>
       </c>
       <c r="B40" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$42,A40)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$43,A40)</f>
         <v/>
       </c>
     </row>
@@ -5276,7 +5382,7 @@
         </is>
       </c>
       <c r="B41" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$42,A41)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$43,A41)</f>
         <v/>
       </c>
     </row>
@@ -5287,7 +5393,7 @@
         </is>
       </c>
       <c r="B42" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$42,A42)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$43,A42)</f>
         <v/>
       </c>
     </row>
